--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_occupation/lang_occupation__name_title__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_occupation/lang_occupation__name_title__part_0001.xlsx
@@ -1,138 +1,50 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="translation" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'translation'!$A$1:$N$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
-  <si>
-    <t>split_id</t>
-  </si>
-  <si>
-    <t>prompt_domain</t>
-  </si>
-  <si>
-    <t>prompt_file</t>
-  </si>
-  <si>
-    <t>source_file</t>
-  </si>
-  <si>
-    <t>original_index</t>
-  </si>
-  <si>
-    <t>database</t>
-  </si>
-  <si>
-    <t>table</t>
-  </si>
-  <si>
-    <t>primary_key_column</t>
-  </si>
-  <si>
-    <t>primary_key</t>
-  </si>
-  <si>
-    <t>column</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>source_en</t>
-  </si>
-  <si>
-    <t>new_translation_vi</t>
-  </si>
-  <si>
-    <t>translator_note</t>
-  </si>
-  <si>
-    <t>NAME_TITLE_0058592</t>
-  </si>
-  <si>
-    <t>NAME_TITLE_0058593</t>
-  </si>
-  <si>
-    <t>name_title</t>
-  </si>
-  <si>
-    <t>name_title_prompt.md</t>
-  </si>
-  <si>
-    <t>lang_occupation.json</t>
-  </si>
-  <si>
-    <t>lang_occupation.db</t>
-  </si>
-  <si>
-    <t>OccupationConfig</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Content</t>
-  </si>
-  <si>
-    <t>general</t>
-  </si>
-  <si>
-    <t>An'ke</t>
-  </si>
-  <si>
-    <t>Yangyang</t>
-  </si>
-  <si>
-    <t>keep_proper_name</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -140,36 +52,91 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -457,143 +424,244 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="12" max="12"/>
+    <col width="80" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>split_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>prompt_domain</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>prompt_file</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>source_file</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>original_index</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>primary_key_column</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>primary_key</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>source_en</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>new_translation_vi</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>translator_note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>NAME_TITLE_0058592</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>name_title</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>name_title_prompt.md</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>lang_occupation.json</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>lang_occupation.db</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>OccupationConfig</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>An'ke</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>An'ke</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>keep_proper_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>NAME_TITLE_0058593</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>name_title</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>name_title_prompt.md</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>lang_occupation.json</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" t="s">
-        <v>28</v>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>lang_occupation.db</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>OccupationConfig</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Yangyang</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Yangyang</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>keep_proper_name</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <autoFilter ref="A1:N3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>